--- a/tools/importer/reports/import-foundation-home.report.xlsx
+++ b/tools/importer/reports/import-foundation-home.report.xlsx
@@ -127,7 +127,7 @@
     <t>en/home/what-we-do</t>
   </si>
   <si>
-    <t>2026-04-30T00:17:49.195Z</t>
+    <t>2026-04-30T21:47:41.950Z</t>
   </si>
   <si>
     <t>What We Do</t>
